--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>103.1125964757935</v>
+        <v>16.75579692731644</v>
       </c>
       <c r="D2" t="n">
-        <v>102.957490732628</v>
+        <v>16.73059224405205</v>
       </c>
       <c r="E2" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F2" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>110.0501650890757</v>
+        <v>17.8831518269748</v>
       </c>
       <c r="D3" t="n">
-        <v>111.5861697335412</v>
+        <v>18.13275258170044</v>
       </c>
       <c r="E3" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F3" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>126.7677821783906</v>
+        <v>20.59976460398848</v>
       </c>
       <c r="D4" t="n">
-        <v>127.5833252584363</v>
+        <v>20.7322903544959</v>
       </c>
       <c r="E4" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F4" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>92.88697168092116</v>
+        <v>15.09413289814969</v>
       </c>
       <c r="D5" t="n">
-        <v>82.20721320655065</v>
+        <v>13.35867214606448</v>
       </c>
       <c r="E5" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F5" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>117.4228868266522</v>
+        <v>19.08121910933098</v>
       </c>
       <c r="D6" t="n">
-        <v>118.3186595616594</v>
+        <v>19.22678217876966</v>
       </c>
       <c r="E6" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F6" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>133.3063082078771</v>
+        <v>21.66227508378002</v>
       </c>
       <c r="D7" t="n">
-        <v>133.719300575533</v>
+        <v>21.72938634352411</v>
       </c>
       <c r="E7" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F7" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>138.1046397585393</v>
+        <v>22.44200396076264</v>
       </c>
       <c r="D8" t="n">
-        <v>138.2856024330565</v>
+        <v>22.47141039537167</v>
       </c>
       <c r="E8" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F8" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>92.51883957838167</v>
+        <v>15.03431143148702</v>
       </c>
       <c r="D9" t="n">
-        <v>65.37202280940109</v>
+        <v>10.62295370652768</v>
       </c>
       <c r="E9" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F9" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>109.9639913721203</v>
+        <v>17.86914859796955</v>
       </c>
       <c r="D10" t="n">
-        <v>111.1149950426258</v>
+        <v>18.0561866944267</v>
       </c>
       <c r="E10" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F10" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>117.6333936873549</v>
+        <v>19.11542647419517</v>
       </c>
       <c r="D11" t="n">
-        <v>118.3455677784771</v>
+        <v>19.23115476400252</v>
       </c>
       <c r="E11" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F11" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>103.0222646203361</v>
+        <v>16.74111800080461</v>
       </c>
       <c r="D12" t="n">
-        <v>104.4556338465088</v>
+        <v>16.97404050005768</v>
       </c>
       <c r="E12" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F12" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>89.3313834149279</v>
+        <v>14.51634980492578</v>
       </c>
       <c r="D13" t="n">
-        <v>84.9776323928548</v>
+        <v>13.80886526383891</v>
       </c>
       <c r="E13" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>138.0369714038187</v>
+        <v>22.43100785312053</v>
       </c>
       <c r="D14" t="n">
-        <v>138.0135227471959</v>
+        <v>22.42719744641933</v>
       </c>
       <c r="E14" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F14" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>85.86196038840856</v>
+        <v>13.95256856311639</v>
       </c>
       <c r="D15" t="n">
-        <v>64.49443994108272</v>
+        <v>10.48034649042594</v>
       </c>
       <c r="E15" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F15" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>88.84109779474331</v>
+        <v>14.43667839164579</v>
       </c>
       <c r="D16" t="n">
-        <v>90.4080703958093</v>
+        <v>14.69131143931901</v>
       </c>
       <c r="E16" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F16" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>93.42321667674132</v>
+        <v>15.18127270997046</v>
       </c>
       <c r="D17" t="n">
-        <v>94.69053849218461</v>
+        <v>15.38721250498</v>
       </c>
       <c r="E17" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F17" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>100.9510928829658</v>
+        <v>16.40455259348195</v>
       </c>
       <c r="D18" t="n">
-        <v>101.75857669471</v>
+        <v>16.53576871289038</v>
       </c>
       <c r="E18" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F18" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>73.53474310813048</v>
+        <v>11.9493957550712</v>
       </c>
       <c r="D19" t="n">
-        <v>56.8407362264613</v>
+        <v>9.236619636799961</v>
       </c>
       <c r="E19" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F19" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>83.04803768795216</v>
+        <v>13.49530612429223</v>
       </c>
       <c r="D20" t="n">
-        <v>84.80887615614708</v>
+        <v>13.7814423753739</v>
       </c>
       <c r="E20" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F20" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1115095174414</v>
+        <v>17.73062029658423</v>
       </c>
       <c r="D21" t="n">
-        <v>109.497835438788</v>
+        <v>17.79339825880304</v>
       </c>
       <c r="E21" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F21" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>69.94012583487154</v>
+        <v>11.36527044816662</v>
       </c>
       <c r="D22" t="n">
-        <v>47.03163889010613</v>
+        <v>7.642641319642246</v>
       </c>
       <c r="E22" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F22" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>80.02740230163285</v>
+        <v>13.00445287401534</v>
       </c>
       <c r="D23" t="n">
-        <v>81.36483425237604</v>
+        <v>13.22178556601111</v>
       </c>
       <c r="E23" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F23" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>102.8041031107959</v>
+        <v>16.70566675550433</v>
       </c>
       <c r="D24" t="n">
-        <v>103.0185796291446</v>
+        <v>16.74051918973599</v>
       </c>
       <c r="E24" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F24" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>115.0121230995583</v>
+        <v>18.68947000367823</v>
       </c>
       <c r="D25" t="n">
-        <v>114.9012884502014</v>
+        <v>18.67145937315773</v>
       </c>
       <c r="E25" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F25" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>126.2621793601328</v>
+        <v>20.51760414602158</v>
       </c>
       <c r="D26" t="n">
-        <v>125.9035350149573</v>
+        <v>20.45932443993056</v>
       </c>
       <c r="E26" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F26" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>65.12631317802253</v>
+        <v>10.58302589142866</v>
       </c>
       <c r="D27" t="n">
-        <v>60.85737587805305</v>
+        <v>9.889323580183621</v>
       </c>
       <c r="E27" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F27" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>89.23146873822932</v>
+        <v>14.50011366996227</v>
       </c>
       <c r="D28" t="n">
-        <v>89.64547309526131</v>
+        <v>14.56738937797996</v>
       </c>
       <c r="E28" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F28" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>68.43228364819377</v>
+        <v>11.12024609283149</v>
       </c>
       <c r="D29" t="n">
-        <v>38.67862112331741</v>
+        <v>6.285275932539078</v>
       </c>
       <c r="E29" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F29" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>81.68739033447004</v>
+        <v>13.27420092935138</v>
       </c>
       <c r="D30" t="n">
-        <v>82.4502330433111</v>
+        <v>13.39816286953806</v>
       </c>
       <c r="E30" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F30" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>53.56824693351373</v>
+        <v>8.704840126695983</v>
       </c>
       <c r="D31" t="n">
-        <v>41.80053325615436</v>
+        <v>6.792586654125084</v>
       </c>
       <c r="E31" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F31" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>62.71882874686575</v>
+        <v>10.19180967136568</v>
       </c>
       <c r="D32" t="n">
-        <v>64.64464388310512</v>
+        <v>10.50475463100458</v>
       </c>
       <c r="E32" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F32" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>122.3581805458333</v>
+        <v>19.88320433869791</v>
       </c>
       <c r="D33" t="n">
-        <v>121.5566126595758</v>
+        <v>19.75294955718108</v>
       </c>
       <c r="E33" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F33" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>65.15212987565742</v>
+        <v>10.58722110479433</v>
       </c>
       <c r="D34" t="n">
-        <v>66.35616395326356</v>
+        <v>10.78287664240533</v>
       </c>
       <c r="E34" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F34" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>115.0933833680445</v>
+        <v>18.70267479730724</v>
       </c>
       <c r="D35" t="n">
-        <v>114.3039631931981</v>
+        <v>18.57439401889469</v>
       </c>
       <c r="E35" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F35" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>72.35469676821687</v>
+        <v>11.75763822483524</v>
       </c>
       <c r="D36" t="n">
-        <v>72.70109671471373</v>
+        <v>11.81392821614098</v>
       </c>
       <c r="E36" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F36" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>88.1994403662449</v>
+        <v>14.3324090595148</v>
       </c>
       <c r="D37" t="n">
-        <v>87.99721828790692</v>
+        <v>14.29954797178488</v>
       </c>
       <c r="E37" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F37" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>103.2301589313102</v>
+        <v>16.77490082633791</v>
       </c>
       <c r="D38" t="n">
-        <v>102.6454777619059</v>
+        <v>16.67989013630971</v>
       </c>
       <c r="E38" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F38" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>63.29164857756918</v>
+        <v>10.28489289385499</v>
       </c>
       <c r="D39" t="n">
-        <v>63.5516927148221</v>
+        <v>10.32715006615859</v>
       </c>
       <c r="E39" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F39" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>42.89318238648522</v>
+        <v>6.970142137803848</v>
       </c>
       <c r="D40" t="n">
-        <v>44.87649295373283</v>
+        <v>7.292430104981585</v>
       </c>
       <c r="E40" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F40" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>53.2585650553665</v>
+        <v>8.654516821497056</v>
       </c>
       <c r="D41" t="n">
-        <v>54.02662973312281</v>
+        <v>8.779327331632457</v>
       </c>
       <c r="E41" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F41" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>38.4443355706707</v>
+        <v>6.247204530233988</v>
       </c>
       <c r="D42" t="n">
-        <v>32.49965106855716</v>
+        <v>5.281193298640539</v>
       </c>
       <c r="E42" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F42" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>87.64676269278952</v>
+        <v>14.2425989375783</v>
       </c>
       <c r="D43" t="n">
-        <v>86.90565805220342</v>
+        <v>14.12216943348306</v>
       </c>
       <c r="E43" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F43" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>78.78525557869848</v>
+        <v>12.8026040315385</v>
       </c>
       <c r="D44" t="n">
-        <v>78.17517177549306</v>
+        <v>12.70346541351762</v>
       </c>
       <c r="E44" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F44" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>117.085392964807</v>
+        <v>19.02637635678115</v>
       </c>
       <c r="D45" t="n">
-        <v>115.9013897762558</v>
+        <v>18.83397583864156</v>
       </c>
       <c r="E45" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F45" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>100.4933989058763</v>
+        <v>16.3301773222049</v>
       </c>
       <c r="D46" t="n">
-        <v>99.29563183551474</v>
+        <v>16.13554017327115</v>
       </c>
       <c r="E46" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F46" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>45.87597058058799</v>
+        <v>7.454845219345549</v>
       </c>
       <c r="D47" t="n">
-        <v>46.12536202129006</v>
+        <v>7.495371328459635</v>
       </c>
       <c r="E47" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F47" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>65.39774567704296</v>
+        <v>10.62713367251948</v>
       </c>
       <c r="D48" t="n">
-        <v>64.70037327743408</v>
+        <v>10.51381065758304</v>
       </c>
       <c r="E48" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F48" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>92.90309907389407</v>
+        <v>15.09675359950779</v>
       </c>
       <c r="D49" t="n">
-        <v>91.53026353177601</v>
+        <v>14.8736678239136</v>
       </c>
       <c r="E49" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F49" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>85.20600213692882</v>
+        <v>13.84597534725093</v>
       </c>
       <c r="D50" t="n">
-        <v>83.68640500043358</v>
+        <v>13.59904081257046</v>
       </c>
       <c r="E50" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F50" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>105.2048440619192</v>
+        <v>17.09578716006188</v>
       </c>
       <c r="D51" t="n">
-        <v>103.3823067867059</v>
+        <v>16.7996248528397</v>
       </c>
       <c r="E51" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F51" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>56.31360093606205</v>
+        <v>9.150960152110084</v>
       </c>
       <c r="D52" t="n">
-        <v>55.49181462243772</v>
+        <v>9.017419876146128</v>
       </c>
       <c r="E52" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F52" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>96.83884682146019</v>
+        <v>15.73631260848728</v>
       </c>
       <c r="D53" t="n">
-        <v>94.95760619472193</v>
+        <v>15.43061100664231</v>
       </c>
       <c r="E53" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F53" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>75.4096963659688</v>
+        <v>12.25407565946993</v>
       </c>
       <c r="D54" t="n">
-        <v>73.79087044703687</v>
+        <v>11.99101644764349</v>
       </c>
       <c r="E54" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F54" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>101.3142747463132</v>
+        <v>16.46356964627589</v>
       </c>
       <c r="D55" t="n">
-        <v>99.25917671968982</v>
+        <v>16.1296162169496</v>
       </c>
       <c r="E55" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F55" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>49.32068371898392</v>
+        <v>8.014611104334888</v>
       </c>
       <c r="D56" t="n">
-        <v>47.50174005385628</v>
+        <v>7.719032758751646</v>
       </c>
       <c r="E56" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F56" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>76.14172052694322</v>
+        <v>12.37302958562827</v>
       </c>
       <c r="D57" t="n">
-        <v>74.08405305017689</v>
+        <v>12.03865862065375</v>
       </c>
       <c r="E57" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F57" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>82.46966009192377</v>
+        <v>13.40131976493761</v>
       </c>
       <c r="D58" t="n">
-        <v>80.29156249738507</v>
+        <v>13.04737890582508</v>
       </c>
       <c r="E58" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F58" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>66.33332250956768</v>
+        <v>10.77916490780475</v>
       </c>
       <c r="D59" t="n">
-        <v>64.03909534854621</v>
+        <v>10.40635299413876</v>
       </c>
       <c r="E59" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F59" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>93.33773722081857</v>
+        <v>15.16738229838302</v>
       </c>
       <c r="D60" t="n">
-        <v>91.01194009105998</v>
+        <v>14.78944026479725</v>
       </c>
       <c r="E60" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F60" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>100.8199569643306</v>
+        <v>16.38324300670372</v>
       </c>
       <c r="D61" t="n">
-        <v>98.38137226977483</v>
+        <v>15.98697299383841</v>
       </c>
       <c r="E61" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F61" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>110.6505052234668</v>
+        <v>17.98070709881336</v>
       </c>
       <c r="D62" t="n">
-        <v>108.1600844304399</v>
+        <v>17.57601371994649</v>
       </c>
       <c r="E62" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F62" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>85.41169527063681</v>
+        <v>13.87940048147848</v>
       </c>
       <c r="D63" t="n">
-        <v>82.7126549863864</v>
+        <v>13.44080643528779</v>
       </c>
       <c r="E63" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F63" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>103.8456269977905</v>
+        <v>16.87491438714096</v>
       </c>
       <c r="D64" t="n">
-        <v>101.0821278550782</v>
+        <v>16.4258457764502</v>
       </c>
       <c r="E64" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F64" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>76.03666450765819</v>
+        <v>12.35595798249446</v>
       </c>
       <c r="D65" t="n">
-        <v>72.82538674043164</v>
+        <v>11.83412534532014</v>
       </c>
       <c r="E65" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F65" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>90.53327558877233</v>
+        <v>14.7116572831755</v>
       </c>
       <c r="D66" t="n">
-        <v>87.44112535059976</v>
+        <v>14.20918286947246</v>
       </c>
       <c r="E66" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F66" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>75.84254405465911</v>
+        <v>12.32441340888211</v>
       </c>
       <c r="D67" t="n">
-        <v>72.16761250769549</v>
+        <v>11.72723703250052</v>
       </c>
       <c r="E67" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F67" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>66.79268996849524</v>
+        <v>10.85381211988048</v>
       </c>
       <c r="D68" t="n">
-        <v>62.92641270077832</v>
+        <v>10.22554206387648</v>
       </c>
       <c r="E68" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F68" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>88.2128326475825</v>
+        <v>14.33458530523216</v>
       </c>
       <c r="D69" t="n">
-        <v>84.62792931856623</v>
+        <v>13.75203851426701</v>
       </c>
       <c r="E69" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F69" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>38.02106063124015</v>
+        <v>6.178422352576526</v>
       </c>
       <c r="D70" t="n">
-        <v>34.92471768781815</v>
+        <v>5.67526662427045</v>
       </c>
       <c r="E70" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F70" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>98.42898968566543</v>
+        <v>15.99471082392063</v>
       </c>
       <c r="D71" t="n">
-        <v>94.89093330080487</v>
+        <v>15.41977666138079</v>
       </c>
       <c r="E71" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F71" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>115.2459132409369</v>
+        <v>18.72746090165224</v>
       </c>
       <c r="D72" t="n">
-        <v>111.8435378620329</v>
+        <v>18.17457490258035</v>
       </c>
       <c r="E72" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F72" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>54.07049238991637</v>
+        <v>8.78645501336141</v>
       </c>
       <c r="D73" t="n">
-        <v>49.91732755622224</v>
+        <v>8.111565727886115</v>
       </c>
       <c r="E73" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F73" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>94.41208130278321</v>
+        <v>15.34196321170227</v>
       </c>
       <c r="D74" t="n">
-        <v>90.70479714635141</v>
+        <v>14.7395295362821</v>
       </c>
       <c r="E74" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F74" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>34.72423114812069</v>
+        <v>5.642687561569612</v>
       </c>
       <c r="D75" t="n">
-        <v>34.35508120989196</v>
+        <v>5.582700696607443</v>
       </c>
       <c r="E75" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F75" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>48.8585693476195</v>
+        <v>7.939517518988169</v>
       </c>
       <c r="D76" t="n">
-        <v>44.74298542674724</v>
+        <v>7.270735131846426</v>
       </c>
       <c r="E76" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F76" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>43.02734814740771</v>
+        <v>6.991944073953753</v>
       </c>
       <c r="D77" t="n">
-        <v>43.27809870084975</v>
+        <v>7.032691038888085</v>
       </c>
       <c r="E77" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F77" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>49.8281165040919</v>
+        <v>8.097068931914935</v>
       </c>
       <c r="D78" t="n">
-        <v>47.64259841565532</v>
+        <v>7.74192224254399</v>
       </c>
       <c r="E78" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F78" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>80.74469192421701</v>
+        <v>13.12101243768526</v>
       </c>
       <c r="D79" t="n">
-        <v>76.80422932425488</v>
+        <v>12.48068726519142</v>
       </c>
       <c r="E79" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F79" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>90.08559259383807</v>
+        <v>14.63890879649869</v>
       </c>
       <c r="D80" t="n">
-        <v>86.25382718970398</v>
+        <v>14.0162469183269</v>
       </c>
       <c r="E80" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F80" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>61.43441304826855</v>
+        <v>9.983092120343638</v>
       </c>
       <c r="D81" t="n">
-        <v>57.28868124562012</v>
+        <v>9.30941070241327</v>
       </c>
       <c r="E81" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F81" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>74.12293334036926</v>
+        <v>12.04497666781</v>
       </c>
       <c r="D82" t="n">
-        <v>70.04238554973523</v>
+        <v>11.38188765183198</v>
       </c>
       <c r="E82" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F82" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>53.79040718197557</v>
+        <v>8.74094116707103</v>
       </c>
       <c r="D83" t="n">
-        <v>49.97356808590021</v>
+        <v>8.120704813958785</v>
       </c>
       <c r="E83" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F83" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>69.32306174291141</v>
+        <v>11.2649975332231</v>
       </c>
       <c r="D84" t="n">
-        <v>65.17016466723209</v>
+        <v>10.59015175842521</v>
       </c>
       <c r="E84" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F84" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>117.1238512868996</v>
+        <v>19.03262583412118</v>
       </c>
       <c r="D85" t="n">
-        <v>113.4832717540492</v>
+        <v>18.44103166003299</v>
       </c>
       <c r="E85" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F85" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>128.4697363414208</v>
+        <v>20.87633215548088</v>
       </c>
       <c r="D86" t="n">
-        <v>124.8645064310782</v>
+        <v>20.29048229505021</v>
       </c>
       <c r="E86" t="n">
-        <v>25.07526214911233</v>
+        <v>4.074730099230754</v>
       </c>
       <c r="F86" t="n">
-        <v>26.62666959327461</v>
+        <v>4.326833808907123</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
